--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 07:12:42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 07:12:42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -638,17 +638,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>77224bbb4198e25b0095</t>
+          <t>190458add60f89ffc9bb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>ConsultBae</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer: Proficiency in infrastructure as code (Terraform). Scripting and automation skills (e.g., Python, Shell). Knowing python is must. Collaborate with teams across the company (i.e., network, security, operations) to build complete cloud offerings. Design Disaster Recovery and backup</t>
+          <t xml:space="preserve">Role : DevOps Engineer Experience : 1 to 2 years and 2 to 5 Years as DevOps Engineer (2 Positions) Location : Bangalore. 5 Days Working. Education Qualification : Tech/B.E for Tier-1/Tier-2/Tier-3 Colleges or equivalent institutes Skills :- DevOps Engineering, Ruby On Rails or Python and Bash/Shell </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5211779212?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2160609533?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -678,20 +678,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 07:12:42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>54d34f1e0c5d30e41d21</t>
+          <t>786a48bc23d42af18388</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Terraform</t>
+          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -709,17 +709,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>88e525329cd900ea5f58</t>
+          <t>55a0cfb1bde6bcf1a77d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Ti Steps</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>" GCP Cloud Engineer"</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Job Summary: We are looking for an experienced GCP Cloud Engineer to design, implement, and manage cloud-based solutions on Google Cloud Platform (GCP). The ideal candidate should have expertise in GKE (Google Kubernetes Engine), Cloud Run, Cloud Loadbalancer, Cloud function, Azure DevOps, and Terra</t>
+          <t>Responsibilities : Support CI/CD pipeline setup and maintenance. Automate infrastructure provisioning using tools like Terraform or Ansible. Monitor application performance and system health. Assist in incident response and root cause analysis. Tools &amp; Technologies: Jenkins, GitLab CI/CD, Docker, Ku</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5691797741?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5859122853?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -749,20 +749,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 07:12:42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>d56708496e9a196e2501</t>
+          <t>f2b2d2861a6074dfef26</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>skill:Kubernetes, skill:Terraform, skill:CI/CD</t>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Infrastructure Provisioning</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -780,12 +780,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>190458add60f89ffc9bb</t>
+          <t>1fe33bf1b7159d7e495f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ConsultBae</t>
+          <t>Insight Global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role : DevOps Engineer Experience : 1 to 2 years and 2 to 5 Years as DevOps Engineer (2 Positions) Location : Bangalore. 5 Days Working. Education Qualification : Tech/B.E for Tier-1/Tier-2/Tier-3 Colleges or equivalent institutes Skills :- DevOps Engineering, Ruby On Rails or Python and Bash/Shell </t>
+          <t xml:space="preserve">Job Description Insight Global is seeking a DevOps Engineer for a top enterprise client. This role requires the candidate to be onsite in Bangluru once a week. The ideal candidate will bring deep AWS serverless expertise, strong Terraform and CI/CD experience, and a proven track record within large </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2160609533?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5825362035?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 07:12:42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>786a48bc23d42af18388</t>
+          <t>fcd115af51b90b175ffe</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker</t>
+          <t>skill:AWS, skill:Terraform, skill:CI/CD, skill:Observability</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -847,148 +847,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>55a0cfb1bde6bcf1a77d</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ti Steps</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Responsibilities : Support CI/CD pipeline setup and maintenance. Automate infrastructure provisioning using tools like Terraform or Ansible. Monitor application performance and system health. Assist in incident response and root cause analysis. Tools &amp; Technologies: Jenkins, GitLab CI/CD, Docker, Ku</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/details/5859122853?utm_medium=api&amp;utm_source=447522e9</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-09-03 05:09:46</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-09-03 05:09:46</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>f2b2d2861a6074dfef26</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>90</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Infrastructure Provisioning</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1fe33bf1b7159d7e495f</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Insight Global</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Job Description Insight Global is seeking a DevOps Engineer for a top enterprise client. This role requires the candidate to be onsite in Bangluru once a week. The ideal candidate will bring deep AWS serverless expertise, strong Terraform and CI/CD experience, and a proven track record within large </t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/details/5825362035?utm_medium=api&amp;utm_source=447522e9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-09-03 05:09:46</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-03 05:09:46</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fcd115af51b90b175ffe</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>skill:AWS, skill:Terraform, skill:CI/CD, skill:Observability</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:42</t>
+          <t>2026-09-03 07:32:57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:42</t>
+          <t>2026-09-03 07:32:57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:42</t>
+          <t>2026-09-03 07:32:57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:42</t>
+          <t>2026-09-03 07:32:57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:42</t>
+          <t>2026-09-03 07:32:57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:57</t>
+          <t>2026-09-03 08:49:46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:57</t>
+          <t>2026-09-03 08:49:46</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:57</t>
+          <t>2026-09-03 08:49:46</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:57</t>
+          <t>2026-09-03 08:49:46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:57</t>
+          <t>2026-09-03 08:49:46</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:46</t>
+          <t>2026-09-03 09:26:24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:46</t>
+          <t>2026-09-03 09:26:24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:46</t>
+          <t>2026-09-03 09:26:24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:46</t>
+          <t>2026-09-03 09:26:24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:46</t>
+          <t>2026-09-03 09:26:24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:24</t>
+          <t>2026-09-03 09:50:31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:24</t>
+          <t>2026-09-03 09:50:31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:24</t>
+          <t>2026-09-03 09:50:31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:24</t>
+          <t>2026-09-03 09:50:31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:24</t>
+          <t>2026-09-03 09:50:31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -847,6 +847,77 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4ba1f1a765facaa1c988</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=cloud+engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40007&amp;elckey=-682360204983550915&amp;p=1&amp;aq=3394967998319821153&amp;cid=18943&amp;jobAge=243&amp;brelb=15&amp;bscr=29.78369&amp;scr=29.78369</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:50:31</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:50:31</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2b1b1f1bea326c79719d</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cc65b2d7e8cd0ca2e42c</t>
+          <t>bedebd0e647137fbab9e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3 KUBED CONSULTING INDIA PRIVATE LIMITED</t>
+          <t>Zorba Consulting India</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer Dear Candidate Greetings from 3 Kubed Consulting India Pvt Ltd We are seeking aCloud Engineer with AI MLexpertise to design build and support intelligent applications usingAzure Services Azure AI Foundry Docker and Kubernetes services This is for one of our prestigious clients f</t>
+          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5823128806?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:31</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>eb766d663d9c0ae14e58</t>
+          <t>443a693318c3c6f3b107</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:Kubernetes, skill:Docker</t>
+          <t>skill:Python, skill:FastAPI</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3f74c38a88f9a865435d</t>
+          <t>95ef91cebb610fe29e79</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Xoriant Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Public Cloud Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Description Change the world. Love your job. Texas Instruments is seeking a skilled Public Cloud Engineer to implement, automate, and operate the enterprise public cloud platform across AWS (primary), Azure, and GCP. This role partners with the Public Cloud Architect to execute on platform strategy </t>
+          <t>Role &amp; responsibilities : Development and debugging of applications using Golang or Python. Position Description : Hands-on software development experience in Python or Golang. Strong experience and knowledge of micro services, and distributed systems. Good analytical and debugging skills to root ca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5830626894?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5850370781?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,25 +602,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:31</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45f36ed761a638b42eff</t>
+          <t>59c377651e2ad74ba9c6</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>skill:AWS, skill:Kubernetes, skill:Terraform, skill:CI/CD</t>
+          <t>skill:Python, skill:Distributed Systems</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -638,17 +638,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>190458add60f89ffc9bb</t>
+          <t>cc65b2d7e8cd0ca2e42c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ConsultBae</t>
+          <t>3 KUBED CONSULTING INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role : DevOps Engineer Experience : 1 to 2 years and 2 to 5 Years as DevOps Engineer (2 Positions) Location : Bangalore. 5 Days Working. Education Qualification : Tech/B.E for Tier-1/Tier-2/Tier-3 Colleges or equivalent institutes Skills :- DevOps Engineering, Ruby On Rails or Python and Bash/Shell </t>
+          <t>Azure Cloud Engineer Dear Candidate Greetings from 3 Kubed Consulting India Pvt Ltd We are seeking aCloud Engineer with AI MLexpertise to design build and support intelligent applications usingAzure Services Azure AI Foundry Docker and Kubernetes services This is for one of our prestigious clients f</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2160609533?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5823128806?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -678,20 +678,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:31</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>786a48bc23d42af18388</t>
+          <t>eb766d663d9c0ae14e58</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker</t>
+          <t>skill:Kubernetes, skill:Docker</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -709,17 +709,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>55a0cfb1bde6bcf1a77d</t>
+          <t>3f74c38a88f9a865435d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ti Steps</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Public Cloud Engineer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Responsibilities : Support CI/CD pipeline setup and maintenance. Automate infrastructure provisioning using tools like Terraform or Ansible. Monitor application performance and system health. Assist in incident response and root cause analysis. Tools &amp; Technologies: Jenkins, GitLab CI/CD, Docker, Ku</t>
+          <t xml:space="preserve">Description Change the world. Love your job. Texas Instruments is seeking a skilled Public Cloud Engineer to implement, automate, and operate the enterprise public cloud platform across AWS (primary), Azure, and GCP. This role partners with the Public Cloud Architect to execute on platform strategy </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5859122853?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5830626894?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -749,20 +749,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:31</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>f2b2d2861a6074dfef26</t>
+          <t>45f36ed761a638b42eff</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Infrastructure Provisioning</t>
+          <t>skill:AWS, skill:Kubernetes, skill:Terraform, skill:CI/CD</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -780,12 +780,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1fe33bf1b7159d7e495f</t>
+          <t>190458add60f89ffc9bb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Insight Global</t>
+          <t>ConsultBae</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Job Description Insight Global is seeking a DevOps Engineer for a top enterprise client. This role requires the candidate to be onsite in Bangluru once a week. The ideal candidate will bring deep AWS serverless expertise, strong Terraform and CI/CD experience, and a proven track record within large </t>
+          <t xml:space="preserve">Role : DevOps Engineer Experience : 1 to 2 years and 2 to 5 Years as DevOps Engineer (2 Positions) Location : Bangalore. 5 Days Working. Education Qualification : Tech/B.E for Tier-1/Tier-2/Tier-3 Colleges or equivalent institutes Skills :- DevOps Engineering, Ruby On Rails or Python and Bash/Shell </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5825362035?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2160609533?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:31</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fcd115af51b90b175ffe</t>
+          <t>786a48bc23d42af18388</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>skill:AWS, skill:Terraform, skill:CI/CD, skill:Observability</t>
+          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -851,73 +851,1435 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4ba1f1a765facaa1c988</t>
+          <t>55a0cfb1bde6bcf1a77d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Ti Steps</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Responsibilities : Support CI/CD pipeline setup and maintenance. Automate infrastructure provisioning using tools like Terraform or Ansible. Monitor application performance and system health. Assist in incident response and root cause analysis. Tools &amp; Technologies: Jenkins, GitLab CI/CD, Docker, Ku</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5859122853?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:09:46</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>f2b2d2861a6074dfef26</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Infrastructure Provisioning</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1fe33bf1b7159d7e495f</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Insight Global</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description Insight Global is seeking a DevOps Engineer for a top enterprise client. This role requires the candidate to be onsite in Bangluru once a week. The ideal candidate will bring deep AWS serverless expertise, strong Terraform and CI/CD experience, and a proven track record within large </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5825362035?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:09:46</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fcd115af51b90b175ffe</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Terraform, skill:CI/CD, skill:Observability</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0fa3d588c2f7472524a1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tekskills India Private Limited</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>274b5127202b71d7582d</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ad3b29b4786c6e25b08f</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aliqan Services</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Must have- 1. AWS/Azure(Any one cloud). 2.Ansible / Terraform. 3.Java. 4.Maria DB / MySql. RESPONSIBILITIES:- Site Reliability Engineer - PRIMARY RESPONSIBILITIES OF THIS POSITION SRE team members triage and solve escalations from our care team. This can require debugging production services, invest</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5794938989?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4fd31e180a810aee1d13</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>f5d403ed720a472c876b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wissen Technology</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2 years of hands-on experience in Java development. Strong knowledge of Boto3/Boto AWS libraries (Python). Solid experience with AWS services: EC2, ELB/ALB, CloudWatch. Familiarity with SRE practices and maintenance processes. Strong experience in debugging, troubleshooting, and unit testing. Profic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5211779025?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>03ea2a71e141f631af37</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:AWS, skill:CI/CD, skill:Distributed Systems, skill:Cloud-Native</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>68d177dcd7e961cef2cb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Zensar Technologies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SRE Engineer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Description We are seeking a seasoned Site Reliability Engineering to take end-to-end ownership of our retail eCommerce platform's operational excellence. You will drive SRE culture across engineering teams, champion observability, and work with a cross-functional onsite/offshore team to deliver exc</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5867254752?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1c13ecdc9e7604a73142</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>skill:Kubernetes, skill:Observability</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1e8d90b2f7b27eec4aee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wissen Technology</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SRE Engineer</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Job Description. 1. Cloud experience (Any cloud is fine although AWS is preferred. If non-AWS cloud, then the experience should reflect familiarity with the cloud's common services) 2. Good grasp of Scripting (in Linux for sure ie bash/sh/zsh etc, Windows : nice to have) 3. Python or Java or JS basi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5501134569?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>32b60b6a0297c5084f53</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>50</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Docker, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0d112f518f8db899e3c6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jobdost</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SRE Devops</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Candidates MUST HAVE : Experience with Infrastructure-as-Code tools(IaS) like Terraform and Cloud Formation. Proficiency in cloud-native technologies and architectures (Docker/ Kubernetes), Ci/CD pipelines. Good experience in Javascript. Expertise in Linux / Windows environment. Good Experience in S</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/4344577925?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>08c477bc04ba32062d49</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>80</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Cloud-Native</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0e6b548516e16807909f</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wissen Technology</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Devops/ SRE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The candidate should have a background in development/programming with experience in at least one of the following: .NET, Java (Spring Boot), ReactJS, or AngularJS. Primary Skills: AWS or GCP Cloud DevOps CI/CD pipelines (e.g., Azure DevOps, Jenkins) Python/Bash/PowerShell scripting Secondary Skills</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5211779221?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>48fe7642ecb269a15f16</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:CI/CD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>78a6d7560ddbd4caa774</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3337532b20885bd1775f</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>30</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:Agentic Workflows, skill:MCP</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>f65350a6483821dfdd3a</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1463f44c91d7b4c9c45f</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>30</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>skill:Observability, skill:RAG, skill:MCP</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fe444d035cdcafe996e0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VY SYSTEMS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cloud Operations Engineer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>You have strong experience supporting cloud environments within the AWS platform. * You have hands-on experience with cloud platforms, Docker, Kubernetes, Jenkins, Terraform, Artifactory, infrastructure automation, CI/CD pipelines, monitoring, and operational support in enterprise environments. * Yo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5812187960?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8642e0db63a1b35f0d71</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>46a75a4c0c9726c2e182</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Merkle Science</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Software Engineer(Intern)- Backend</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...several others. 
+ Responsibilities 
+ Design, build, and maintain &lt;b&gt;backend &lt;/b&gt;services and REST APIs using  Python(Django/FastAPI)
+ Write...&amp;nbsp;&amp;nbsp;...service performance 
+ Collaborate with frontend and QA &lt;b&gt;engineers &lt;/b&gt;to ship end-to-end features 
+ Write clean, tested, well-d</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=12&amp;groupId=41745&amp;elckey=556603733564230260&amp;p=1&amp;aq=-755282716108339557&amp;cid=18943&amp;jobAge=654&amp;brelb=15&amp;bscr=57.927845&amp;scr=57.927845</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>68457383d022598649bc</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:FastAPI, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>80952a5c525d0edce5ac</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Smartworking</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Cloud Engineer (Backend / DevOps-leaning)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  Cloud &lt;b&gt;Engineer (Backend &lt;/b&gt;/ DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=246&amp;brelb=15&amp;scr=57.48293&amp;bscr=57.48293&amp;aq=-755282716108339557&amp;elckey=556603733564230260</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>f2f309d2c133a2334dd5</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>eceda26c725067d42a0c</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sophos</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...development of next-generation web applications, UI frameworks, and &lt;b&gt;developer &lt;/b&gt;platforms. The ideal candidate should have strong experience in...&amp;nbsp;&amp;nbsp;.... 
+ Strong development experience in  Java  ,  Go  , or  &lt;b&gt;Python &lt;/b&gt; . 
+ Experience building  RESTful APIs  ,  microserv</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=-4647303329973737492&amp;p=1&amp;aq=-496784137792444050&amp;cid=18943&amp;jobAge=894&amp;brelb=15&amp;bscr=53.345592&amp;scr=53.345592</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5537fa1f7e5e07c1c9a1</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Microservices</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>e9964687b1fe4743bd14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Merkle Science</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Software Engineer(Intern)- Backend</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
+ Responsibilities 
+ Design, build, and maintain backend services and REST APIs using  &lt;b&gt;Python(&lt;/b&gt;Django/FastAPI)
+ Write efficient queries and manage data models in  PostgreSQL 
+ Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=3&amp;groupId=40830&amp;elckey=-4647303329973737492&amp;p=1&amp;aq=-496784137792444050&amp;cid=18943&amp;jobAge=654&amp;brelb=15&amp;bscr=53.164566&amp;scr=53.164566</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>c88e76ee05d5f22f3af4</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:FastAPI, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>45e7a14ef0b959af0fa4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=cloud+engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40007&amp;elckey=-682360204983550915&amp;p=1&amp;aq=3394967998319821153&amp;cid=18943&amp;jobAge=243&amp;brelb=15&amp;bscr=29.78369&amp;scr=29.78369</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Engineer&amp;rgn=55126&amp;pos=11&amp;groupId=40007&amp;elckey=4713805581606040439&amp;p=1&amp;aq=-8501492801892585007&amp;cid=18943&amp;jobAge=246&amp;brelb=15&amp;bscr=30.0431&amp;scr=30.0431</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-09-03 09:50:31</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-09-03 09:50:31</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>2b1b1f1bea326c79719d</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K23" t="n">
         <v>20</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>skill:AWS, skill:Terraform</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8094910c044e97c88e2d</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  Cloud &lt;b&gt;Engineer &lt;/b&gt;(Backend / &lt;b&gt;DevOps-&lt;/b&gt;leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nb</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=10&amp;rgn=55126&amp;cid=18943&amp;ckey=DevOps+Engineer&amp;jobAge=246&amp;brelb=15&amp;scr=30.998257&amp;bscr=30.998257&amp;aq=2610027689483361517&amp;elckey=1981552223296789602</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>d322ed2c3af201959570</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>48b30f1e0bbf5508138f</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ping Identity</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...of distributed systems capable of handling rapid global growth while maintaining low latency. 
+ Operational Excellence: Partner with &lt;b&gt;SRE &lt;/b&gt;and DevOps to enhance CI/CD pipelines, automated scaling, and self-healing infrastructure. 
+ Technical Leadership: Drive rigorous...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=-1454816734404100747&amp;p=1&amp;aq=534615877913273033&amp;cid=18943&amp;jobAge=54&amp;relb=100&amp;brelb=100&amp;bscr=737.42896&amp;scr=737.42896</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>c83d35754b7c640725c4</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>skill:CI/CD, skill:Distributed Systems</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0c7f8bd7dd21b66a522e</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Operations+Engineer&amp;rgn=55126&amp;pos=15&amp;groupId=73040043&amp;elckey=-1226164450022596303&amp;p=1&amp;aq=4440872342391108350&amp;cid=18943&amp;jobAge=246&amp;brelb=15&amp;bscr=29.93273&amp;scr=29.93273</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:36</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2b1b1f1bea326c79719d</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>20</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>skill:AWS, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46a75a4c0c9726c2e182</t>
+          <t>1951016e1d0f427a00f1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=12&amp;groupId=41745&amp;elckey=556603733564230260&amp;p=1&amp;aq=-755282716108339557&amp;cid=18943&amp;jobAge=654&amp;brelb=15&amp;bscr=57.927845&amp;scr=57.927845</t>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-4868270844738951049&amp;p=1&amp;aq=5350709870888437717&amp;cid=18943&amp;jobAge=655&amp;brelb=15&amp;bscr=57.969448&amp;scr=57.969448</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>80952a5c525d0edce5ac</t>
+          <t>816d73c6df569bab656d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=246&amp;brelb=15&amp;scr=57.48293&amp;bscr=57.48293&amp;aq=-755282716108339557&amp;elckey=556603733564230260</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=247&amp;brelb=15&amp;scr=57.88233&amp;bscr=57.88233&amp;aq=5350709870888437717&amp;elckey=-4868270844738951049</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>eceda26c725067d42a0c</t>
+          <t>d345e7e0b563a35cb88b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=-4647303329973737492&amp;p=1&amp;aq=-496784137792444050&amp;cid=18943&amp;jobAge=894&amp;brelb=15&amp;bscr=53.345592&amp;scr=53.345592</t>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=8374566165432632815&amp;p=1&amp;aq=1379403374137944561&amp;cid=18943&amp;jobAge=895&amp;brelb=15&amp;bscr=53.79139&amp;scr=53.79139</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e9964687b1fe4743bd14</t>
+          <t>f01ec362a8f762b57277</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=3&amp;groupId=40830&amp;elckey=-4647303329973737492&amp;p=1&amp;aq=-496784137792444050&amp;cid=18943&amp;jobAge=654&amp;brelb=15&amp;bscr=53.164566&amp;scr=53.164566</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=655&amp;brelb=15&amp;scr=53.224674&amp;bscr=53.224674&amp;aq=1379403374137944561&amp;elckey=8374566165432632815</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45e7a14ef0b959af0fa4</t>
+          <t>187df91d921d1d45e53d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Engineer&amp;rgn=55126&amp;pos=11&amp;groupId=40007&amp;elckey=4713805581606040439&amp;p=1&amp;aq=-8501492801892585007&amp;cid=18943&amp;jobAge=246&amp;brelb=15&amp;bscr=30.0431&amp;scr=30.0431</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=247&amp;brelb=15&amp;scr=30.248539&amp;bscr=30.248539&amp;aq=-5592790167043920560&amp;elckey=-4583030252703451422</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2069,7 +2069,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8094910c044e97c88e2d</t>
+          <t>c568c6f9458922308877</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=10&amp;rgn=55126&amp;cid=18943&amp;ckey=DevOps+Engineer&amp;jobAge=246&amp;brelb=15&amp;scr=30.998257&amp;bscr=30.998257&amp;aq=2610027689483361517&amp;elckey=1981552223296789602</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-3443322355006391707&amp;p=1&amp;aq=3471710738178534616&amp;cid=18943&amp;jobAge=247&amp;brelb=15&amp;bscr=31.094933&amp;scr=31.094933</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>48b30f1e0bbf5508138f</t>
+          <t>a0cfa1e08552ef60abe2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=-1454816734404100747&amp;p=1&amp;aq=534615877913273033&amp;cid=18943&amp;jobAge=54&amp;relb=100&amp;brelb=100&amp;bscr=737.42896&amp;scr=737.42896</t>
+          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=7695091504995959008&amp;p=1&amp;aq=5459811397406553746&amp;cid=18943&amp;jobAge=55&amp;relb=100&amp;brelb=100&amp;bscr=736.71344&amp;scr=736.71344</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0c7f8bd7dd21b66a522e</t>
+          <t>b555027704daa35dfd8e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Operations+Engineer&amp;rgn=55126&amp;pos=15&amp;groupId=73040043&amp;elckey=-1226164450022596303&amp;p=1&amp;aq=4440872342391108350&amp;cid=18943&amp;jobAge=246&amp;brelb=15&amp;bscr=29.93273&amp;scr=29.93273</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Operations+Engineer&amp;jobAge=247&amp;brelb=15&amp;scr=30.35093&amp;bscr=30.35093&amp;aq=245524830241379080&amp;elckey=7923743789377463452</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 13:20:58</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1951016e1d0f427a00f1</t>
+          <t>e2478931e8161d3f0b3b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-4868270844738951049&amp;p=1&amp;aq=5350709870888437717&amp;cid=18943&amp;jobAge=655&amp;brelb=15&amp;bscr=57.969448&amp;scr=57.969448</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=656&amp;brelb=15&amp;scr=57.430958&amp;bscr=57.430958&amp;aq=78407544719955596&amp;elckey=-5712181725608664146</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>816d73c6df569bab656d</t>
+          <t>cedb7a2c4f4c6323bee6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=247&amp;brelb=15&amp;scr=57.88233&amp;bscr=57.88233&amp;aq=5350709870888437717&amp;elckey=-4868270844738951049</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=41745&amp;elckey=-5712181725608664146&amp;p=1&amp;aq=78407544719955596&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=57.147484&amp;scr=57.147484</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>d345e7e0b563a35cb88b</t>
+          <t>f0bb650aa51f5688cfe7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=8374566165432632815&amp;p=1&amp;aq=1379403374137944561&amp;cid=18943&amp;jobAge=895&amp;brelb=15&amp;bscr=53.79139&amp;scr=53.79139</t>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=7530655284562919718&amp;p=1&amp;aq=7257076090002218037&amp;cid=18943&amp;jobAge=896&amp;brelb=15&amp;bscr=53.270027&amp;scr=53.270027</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f01ec362a8f762b57277</t>
+          <t>2d29b6ac018708578c30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=655&amp;brelb=15&amp;scr=53.224674&amp;bscr=53.224674&amp;aq=1379403374137944561&amp;elckey=8374566165432632815</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=656&amp;brelb=15&amp;scr=52.80803&amp;bscr=52.80803&amp;aq=7257076090002218037&amp;elckey=7530655284562919718</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>187df91d921d1d45e53d</t>
+          <t>a5f90a7e5f0818bfdcf2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=247&amp;brelb=15&amp;scr=30.248539&amp;bscr=30.248539&amp;aq=-5592790167043920560&amp;elckey=-4583030252703451422</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=29.701124&amp;bscr=29.701124&amp;aq=5876952964847405562&amp;elckey=1681426100375779297</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2069,7 +2069,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>c568c6f9458922308877</t>
+          <t>c3a5b21e0de5e56af077</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-3443322355006391707&amp;p=1&amp;aq=3471710738178534616&amp;cid=18943&amp;jobAge=247&amp;brelb=15&amp;bscr=31.094933&amp;scr=31.094933</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-4287233235876104804&amp;p=1&amp;aq=4168375251313279643&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=30.79606&amp;scr=30.79606</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a0cfa1e08552ef60abe2</t>
+          <t>f9201c3dd6b1a91aa95a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=7695091504995959008&amp;p=1&amp;aq=5459811397406553746&amp;cid=18943&amp;jobAge=55&amp;relb=100&amp;brelb=100&amp;bscr=736.71344&amp;scr=736.71344</t>
+          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=-4487196215634361889&amp;p=1&amp;aq=388710658763944487&amp;cid=18943&amp;jobAge=56&amp;relb=100&amp;brelb=100&amp;bscr=737.72626&amp;scr=737.72626</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>b555027704daa35dfd8e</t>
+          <t>4bd1fea6480c641707f1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Operations+Engineer&amp;jobAge=247&amp;brelb=15&amp;scr=30.35093&amp;bscr=30.35093&amp;aq=245524830241379080&amp;elckey=7923743789377463452</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Operations+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=29.775251&amp;bscr=29.775251&amp;aq=3994044870557838627&amp;elckey=-4258543931252857445</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:58</t>
+          <t>2026-09-03 14:44:18</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>e2478931e8161d3f0b3b</t>
+          <t>2a726ebdd0afb961886f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=656&amp;brelb=15&amp;scr=57.430958&amp;bscr=57.430958&amp;aq=78407544719955596&amp;elckey=-5712181725608664146</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=658&amp;brelb=15&amp;scr=56.879696&amp;bscr=56.879696&amp;aq=1154262406179503089&amp;elckey=-3285534042292215138</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cedb7a2c4f4c6323bee6</t>
+          <t>fadd47742aea28683ddb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=41745&amp;elckey=-5712181725608664146&amp;p=1&amp;aq=78407544719955596&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=57.147484&amp;scr=57.147484</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=56.544323&amp;bscr=56.544323&amp;aq=1154262406179503089&amp;elckey=-3285534042292215138</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f0bb650aa51f5688cfe7</t>
+          <t>d8be0b295d201239d903</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=7530655284562919718&amp;p=1&amp;aq=7257076090002218037&amp;cid=18943&amp;jobAge=896&amp;brelb=15&amp;bscr=53.270027&amp;scr=53.270027</t>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=-8489441105830182890&amp;p=1&amp;aq=8882276308265068022&amp;cid=18943&amp;jobAge=898&amp;brelb=15&amp;bscr=52.631203&amp;scr=52.631203</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2d29b6ac018708578c30</t>
+          <t>86c0e51a3b6654fd7b72</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=656&amp;brelb=15&amp;scr=52.80803&amp;bscr=52.80803&amp;aq=7257076090002218037&amp;elckey=7530655284562919718</t>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=-8489441105830182890&amp;p=1&amp;aq=8882276308265068022&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=52.072277&amp;scr=52.072277</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a5f90a7e5f0818bfdcf2</t>
+          <t>65775a6b0ef427ea49eb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=29.701124&amp;bscr=29.701124&amp;aq=5876952964847405562&amp;elckey=1681426100375779297</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=28.985275&amp;bscr=28.985275&amp;aq=-8809178904638934262&amp;elckey=8668378667461621585</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2069,7 +2069,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>c3a5b21e0de5e56af077</t>
+          <t>235ab6b4e3ed60f55361</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-4287233235876104804&amp;p=1&amp;aq=4168375251313279643&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=30.79606&amp;scr=30.79606</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-1860585552559655796&amp;p=1&amp;aq=4586418624418592339&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=30.378479&amp;scr=30.378479</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f9201c3dd6b1a91aa95a</t>
+          <t>142e4ba47d0fd3e86456</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=-4487196215634361889&amp;p=1&amp;aq=388710658763944487&amp;cid=18943&amp;jobAge=56&amp;relb=100&amp;brelb=100&amp;bscr=737.72626&amp;scr=737.72626</t>
+          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=3&amp;elckey=2499756351451480399&amp;p=1&amp;aq=7822845172208213070&amp;cid=18943&amp;jobAge=58&amp;relb=100&amp;brelb=100&amp;bscr=725.0664&amp;scr=725.0664</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4bd1fea6480c641707f1</t>
+          <t>bcf58527fb7e7facba85</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Operations+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=29.775251&amp;bscr=29.775251&amp;aq=3994044870557838627&amp;elckey=-4258543931252857445</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Operations+Engineer&amp;rgn=55126&amp;pos=15&amp;groupId=73040043&amp;elckey=2728408635832984843&amp;p=1&amp;aq=8381010108530996913&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=29.177908&amp;scr=29.177908</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 14:44:18</t>
+          <t>2026-09-03 16:32:06</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/data/varshini_jobs.xlsx
+++ b/data/varshini_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,12 +496,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bedebd0e647137fbab9e</t>
+          <t>95ef91cebb610fe29e79</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zorba Consulting India</t>
+          <t>Xoriant Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+          <t>Role &amp; responsibilities : Development and debugging of applications using Golang or Python. Position Description : Hands-on software development experience in Python or Golang. Strong experience and knowledge of micro services, and distributed systems. Good analytical and debugging skills to root ca</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5850370781?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>443a693318c3c6f3b107</t>
+          <t>59c377651e2ad74ba9c6</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:Python, skill:FastAPI</t>
+          <t>skill:Python, skill:Distributed Systems</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>95ef91cebb610fe29e79</t>
+          <t>cc65b2d7e8cd0ca2e42c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Xoriant Corporation</t>
+          <t>3 KUBED CONSULTING INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Role &amp; responsibilities : Development and debugging of applications using Golang or Python. Position Description : Hands-on software development experience in Python or Golang. Strong experience and knowledge of micro services, and distributed systems. Good analytical and debugging skills to root ca</t>
+          <t>Azure Cloud Engineer Dear Candidate Greetings from 3 Kubed Consulting India Pvt Ltd We are seeking aCloud Engineer with AI MLexpertise to design build and support intelligent applications usingAzure Services Azure AI Foundry Docker and Kubernetes services This is for one of our prestigious clients f</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5850370781?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5823128806?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:36</t>
+          <t>2026-09-03 05:09:46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>59c377651e2ad74ba9c6</t>
+          <t>eb766d663d9c0ae14e58</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -620,7 +620,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Distributed Systems</t>
+          <t>skill:Kubernetes, skill:Docker</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -638,17 +638,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cc65b2d7e8cd0ca2e42c</t>
+          <t>3f74c38a88f9a865435d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3 KUBED CONSULTING INDIA PRIVATE LIMITED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Public Cloud Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer Dear Candidate Greetings from 3 Kubed Consulting India Pvt Ltd We are seeking aCloud Engineer with AI MLexpertise to design build and support intelligent applications usingAzure Services Azure AI Foundry Docker and Kubernetes services This is for one of our prestigious clients f</t>
+          <t xml:space="preserve">Description Change the world. Love your job. Texas Instruments is seeking a skilled Public Cloud Engineer to implement, automate, and operate the enterprise public cloud platform across AWS (primary), Azure, and GCP. This role partners with the Public Cloud Architect to execute on platform strategy </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5823128806?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5830626894?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -678,20 +678,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>eb766d663d9c0ae14e58</t>
+          <t>45f36ed761a638b42eff</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>skill:Kubernetes, skill:Docker</t>
+          <t>skill:AWS, skill:Kubernetes, skill:Terraform, skill:CI/CD</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -709,17 +709,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3f74c38a88f9a865435d</t>
+          <t>190458add60f89ffc9bb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>ConsultBae</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Public Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Description Change the world. Love your job. Texas Instruments is seeking a skilled Public Cloud Engineer to implement, automate, and operate the enterprise public cloud platform across AWS (primary), Azure, and GCP. This role partners with the Public Cloud Architect to execute on platform strategy </t>
+          <t xml:space="preserve">Role : DevOps Engineer Experience : 1 to 2 years and 2 to 5 Years as DevOps Engineer (2 Positions) Location : Bangalore. 5 Days Working. Education Qualification : Tech/B.E for Tier-1/Tier-2/Tier-3 Colleges or equivalent institutes Skills :- DevOps Engineering, Ruby On Rails or Python and Bash/Shell </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5830626894?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/2160609533?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45f36ed761a638b42eff</t>
+          <t>786a48bc23d42af18388</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>skill:AWS, skill:Kubernetes, skill:Terraform, skill:CI/CD</t>
+          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -780,17 +780,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>190458add60f89ffc9bb</t>
+          <t>55a0cfb1bde6bcf1a77d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ConsultBae</t>
+          <t>Ti Steps</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role : DevOps Engineer Experience : 1 to 2 years and 2 to 5 Years as DevOps Engineer (2 Positions) Location : Bangalore. 5 Days Working. Education Qualification : Tech/B.E for Tier-1/Tier-2/Tier-3 Colleges or equivalent institutes Skills :- DevOps Engineering, Ruby On Rails or Python and Bash/Shell </t>
+          <t>Responsibilities : Support CI/CD pipeline setup and maintenance. Automate infrastructure provisioning using tools like Terraform or Ansible. Monitor application performance and system health. Assist in incident response and root cause analysis. Tools &amp; Technologies: Jenkins, GitLab CI/CD, Docker, Ku</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/2160609533?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5859122853?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -820,20 +820,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>786a48bc23d42af18388</t>
+          <t>f2b2d2861a6074dfef26</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker</t>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Infrastructure Provisioning</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -851,17 +851,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>55a0cfb1bde6bcf1a77d</t>
+          <t>1fe33bf1b7159d7e495f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ti Steps</t>
+          <t>Insight Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Responsibilities : Support CI/CD pipeline setup and maintenance. Automate infrastructure provisioning using tools like Terraform or Ansible. Monitor application performance and system health. Assist in incident response and root cause analysis. Tools &amp; Technologies: Jenkins, GitLab CI/CD, Docker, Ku</t>
+          <t xml:space="preserve">Job Description Insight Global is seeking a DevOps Engineer for a top enterprise client. This role requires the candidate to be onsite in Bangluru once a week. The ideal candidate will bring deep AWS serverless expertise, strong Terraform and CI/CD experience, and a proven track record within large </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5859122853?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5825362035?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -891,20 +891,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>f2b2d2861a6074dfef26</t>
+          <t>fcd115af51b90b175ffe</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Infrastructure Provisioning</t>
+          <t>skill:AWS, skill:Terraform, skill:CI/CD, skill:Observability</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -922,17 +922,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1fe33bf1b7159d7e495f</t>
+          <t>0fa3d588c2f7472524a1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Insight Global</t>
+          <t>Tekskills India Private Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Job Description Insight Global is seeking a DevOps Engineer for a top enterprise client. This role requires the candidate to be onsite in Bangluru once a week. The ideal candidate will bring deep AWS serverless expertise, strong Terraform and CI/CD experience, and a proven track record within large </t>
+          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5825362035?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -957,25 +957,25 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:46</t>
+          <t>2026-09-03 12:40:36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fcd115af51b90b175ffe</t>
+          <t>274b5127202b71d7582d</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>skill:AWS, skill:Terraform, skill:CI/CD, skill:Observability</t>
+          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker, skill:Terraform</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0fa3d588c2f7472524a1</t>
+          <t>ad3b29b4786c6e25b08f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tekskills India Private Limited</t>
+          <t>Aliqan Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
+          <t>Must have- 1. AWS/Azure(Any one cloud). 2.Ansible / Terraform. 3.Java. 4.Maria DB / MySql. RESPONSIBILITIES:- Site Reliability Engineer - PRIMARY RESPONSIBILITIES OF THIS POSITION SRE team members triage and solve escalations from our care team. This can require debugging production services, invest</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5794938989?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1033,20 +1033,20 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>274b5127202b71d7582d</t>
+          <t>4fd31e180a810aee1d13</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:Kubernetes, skill:Docker, skill:Terraform</t>
+          <t>skill:AWS, skill:Terraform</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1064,12 +1064,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ad3b29b4786c6e25b08f</t>
+          <t>f5d403ed720a472c876b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aliqan Services</t>
+          <t>Wissen Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Must have- 1. AWS/Azure(Any one cloud). 2.Ansible / Terraform. 3.Java. 4.Maria DB / MySql. RESPONSIBILITIES:- Site Reliability Engineer - PRIMARY RESPONSIBILITIES OF THIS POSITION SRE team members triage and solve escalations from our care team. This can require debugging production services, invest</t>
+          <t>2 years of hands-on experience in Java development. Strong knowledge of Boto3/Boto AWS libraries (Python). Solid experience with AWS services: EC2, ELB/ALB, CloudWatch. Familiarity with SRE practices and maintenance processes. Strong experience in debugging, troubleshooting, and unit testing. Profic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5794938989?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5211779025?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4fd31e180a810aee1d13</t>
+          <t>03ea2a71e141f631af37</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>skill:AWS, skill:Terraform</t>
+          <t>skill:Python, skill:AWS, skill:CI/CD, skill:Distributed Systems, skill:Cloud-Native</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1135,17 +1135,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f5d403ed720a472c876b</t>
+          <t>68d177dcd7e961cef2cb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SRE Engineer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2 years of hands-on experience in Java development. Strong knowledge of Boto3/Boto AWS libraries (Python). Solid experience with AWS services: EC2, ELB/ALB, CloudWatch. Familiarity with SRE practices and maintenance processes. Strong experience in debugging, troubleshooting, and unit testing. Profic</t>
+          <t>Description We are seeking a seasoned Site Reliability Engineering to take end-to-end ownership of our retail eCommerce platform's operational excellence. You will drive SRE culture across engineering teams, champion observability, and work with a cross-functional onsite/offshore team to deliver exc</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5211779025?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867254752?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1175,20 +1175,20 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>03ea2a71e141f631af37</t>
+          <t>1c13ecdc9e7604a73142</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>skill:Python, skill:AWS, skill:CI/CD, skill:Distributed Systems, skill:Cloud-Native</t>
+          <t>skill:Kubernetes, skill:Observability</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1206,12 +1206,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>68d177dcd7e961cef2cb</t>
+          <t>1e8d90b2f7b27eec4aee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Wissen Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Description We are seeking a seasoned Site Reliability Engineering to take end-to-end ownership of our retail eCommerce platform's operational excellence. You will drive SRE culture across engineering teams, champion observability, and work with a cross-functional onsite/offshore team to deliver exc</t>
+          <t>Job Description. 1. Cloud experience (Any cloud is fine although AWS is preferred. If non-AWS cloud, then the experience should reflect familiarity with the cloud's common services) 2. Good grasp of Scripting (in Linux for sure ie bash/sh/zsh etc, Windows : nice to have) 3. Python or Java or JS basi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867254752?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5501134569?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1246,20 +1246,20 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1c13ecdc9e7604a73142</t>
+          <t>32b60b6a0297c5084f53</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>skill:Kubernetes, skill:Observability</t>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Docker, skill:Terraform</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1e8d90b2f7b27eec4aee</t>
+          <t>0d112f518f8db899e3c6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Jobdost</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SRE Engineer</t>
+          <t>SRE Devops</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Job Description. 1. Cloud experience (Any cloud is fine although AWS is preferred. If non-AWS cloud, then the experience should reflect familiarity with the cloud's common services) 2. Good grasp of Scripting (in Linux for sure ie bash/sh/zsh etc, Windows : nice to have) 3. Python or Java or JS basi</t>
+          <t>Candidates MUST HAVE : Experience with Infrastructure-as-Code tools(IaS) like Terraform and Cloud Formation. Proficiency in cloud-native technologies and architectures (Docker/ Kubernetes), Ci/CD pipelines. Good experience in Javascript. Expertise in Linux / Windows environment. Good Experience in S</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5501134569?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/4344577925?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1317,20 +1317,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32b60b6a0297c5084f53</t>
+          <t>08c477bc04ba32062d49</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:AWS, skill:Docker, skill:Terraform</t>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Cloud-Native</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1348,17 +1348,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0d112f518f8db899e3c6</t>
+          <t>0e6b548516e16807909f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jobdost</t>
+          <t>Wissen Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SRE Devops</t>
+          <t>Devops/ SRE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Candidates MUST HAVE : Experience with Infrastructure-as-Code tools(IaS) like Terraform and Cloud Formation. Proficiency in cloud-native technologies and architectures (Docker/ Kubernetes), Ci/CD pipelines. Good experience in Javascript. Expertise in Linux / Windows environment. Good Experience in S</t>
+          <t>The candidate should have a background in development/programming with experience in at least one of the following: .NET, Java (Spring Boot), ReactJS, or AngularJS. Primary Skills: AWS or GCP Cloud DevOps CI/CD pipelines (e.g., Azure DevOps, Jenkins) Python/Bash/PowerShell scripting Secondary Skills</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4344577925?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5211779221?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>08c477bc04ba32062d49</t>
+          <t>48fe7642ecb269a15f16</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:AWS, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD, skill:Cloud-Native</t>
+          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:CI/CD</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1419,32 +1419,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0e6b548516e16807909f</t>
+          <t>78a6d7560ddbd4caa774</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Acme Services Private Limited</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Devops/ SRE</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Richmond Town, Bangalore</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The candidate should have a background in development/programming with experience in at least one of the following: .NET, Java (Spring Boot), ReactJS, or AngularJS. Primary Skills: AWS or GCP Cloud DevOps CI/CD pipelines (e.g., Azure DevOps, Jenkins) Python/Bash/PowerShell scripting Secondary Skills</t>
+          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5211779221?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1459,20 +1459,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>48fe7642ecb269a15f16</t>
+          <t>3337532b20885bd1775f</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:CI/CD</t>
+          <t>skill:LLM, skill:Agentic Workflows, skill:MCP</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>78a6d7560ddbd4caa774</t>
+          <t>f65350a6483821dfdd3a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3337532b20885bd1775f</t>
+          <t>1463f44c91d7b4c9c45f</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>skill:LLM, skill:Agentic Workflows, skill:MCP</t>
+          <t>skill:Observability, skill:RAG, skill:MCP</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1561,32 +1561,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f65350a6483821dfdd3a</t>
+          <t>fe444d035cdcafe996e0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acme Services Private Limited</t>
+          <t>VY SYSTEMS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+          <t>You have strong experience supporting cloud environments within the AWS platform. * You have hands-on experience with cloud platforms, Docker, Kubernetes, Jenkins, Terraform, Artifactory, infrastructure automation, CI/CD pipelines, monitoring, and operational support in enterprise environments. * Yo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5812187960?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1601,20 +1601,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1463f44c91d7b4c9c45f</t>
+          <t>8642e0db63a1b35f0d71</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>skill:Observability, skill:RAG, skill:MCP</t>
+          <t>skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1632,96 +1632,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fe444d035cdcafe996e0</t>
+          <t>691c6adea0b4913508a0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VY SYSTEMS PRIVATE LIMITED</t>
+          <t>Merkle Science</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>You have strong experience supporting cloud environments within the AWS platform. * You have hands-on experience with cloud platforms, Docker, Kubernetes, Jenkins, Terraform, Artifactory, infrastructure automation, CI/CD pipelines, monitoring, and operational support in enterprise environments. * Yo</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/details/5812187960?utm_medium=api&amp;utm_source=447522e9</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:40:36</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>8642e0db63a1b35f0d71</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>60</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>skill:AWS, skill:Jenkins, skill:Kubernetes, skill:Docker, skill:Terraform, skill:CI/CD</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2a726ebdd0afb961886f</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Merkle Science</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Software Engineer(Intern)- Backend</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>&amp;nbsp;...several others. 
  Responsibilities 
@@ -1731,9 +1660,80 @@
  Write clean, tested, well-d</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=668&amp;brelb=15&amp;scr=57.15673&amp;bscr=57.15673&amp;aq=-136307116101111113&amp;elckey=-7487284121957792138</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>68457383d022598649bc</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>30</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:FastAPI, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1a2337a62fe753b1d98e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  Cloud &lt;b&gt;Engineer (Backend &lt;/b&gt;/ DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=658&amp;brelb=15&amp;scr=56.879696&amp;bscr=56.879696&amp;aq=1154262406179503089&amp;elckey=-3285534042292215138</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=41745&amp;elckey=-7487284121957792138&amp;p=1&amp;aq=-136307116101111113&amp;cid=18943&amp;jobAge=260&amp;brelb=15&amp;bscr=56.75284&amp;scr=56.75284</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1743,25 +1743,25 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>68457383d022598649bc</t>
+          <t>f2f309d2c133a2334dd5</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>skill:Python, skill:FastAPI, skill:REST APIs</t>
+          <t>skill:AWS, skill:Terraform</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1779,17 +1779,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fadd47742aea28683ddb</t>
+          <t>4358f5fbe1a15ebda396</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smartworking</t>
+          <t>Sophos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1798,150 +1798,79 @@
         </is>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...As a  Cloud &lt;b&gt;Engineer (Backend &lt;/b&gt;/ DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=56.544323&amp;bscr=56.544323&amp;aq=1154262406179503089&amp;elckey=-3285534042292215138</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>f2f309d2c133a2334dd5</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>20</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>skill:AWS, skill:Terraform</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>d8be0b295d201239d903</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sophos</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>&amp;nbsp;...development of next-generation web applications, UI frameworks, and &lt;b&gt;developer &lt;/b&gt;platforms. The ideal candidate should have strong experience in...&amp;nbsp;&amp;nbsp;.... 
  Strong development experience in  Java  ,  Go  , or  &lt;b&gt;Python &lt;/b&gt; . 
  Experience building  RESTful APIs  ,  microserv</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=-8489441105830182890&amp;p=1&amp;aq=8882276308265068022&amp;cid=18943&amp;jobAge=898&amp;brelb=15&amp;bscr=52.631203&amp;scr=52.631203</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=5755552888213791726&amp;p=1&amp;aq=-3369009283499207512&amp;cid=18943&amp;jobAge=908&amp;brelb=15&amp;bscr=53.25766&amp;scr=53.25766</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>5537fa1f7e5e07c1c9a1</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K20" t="n">
         <v>20</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>skill:Python, skill:Microservices</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>86c0e51a3b6654fd7b72</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1362dbe37380d23ef1c6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Merkle Science</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
  Responsibilities 
@@ -1950,9 +1879,80 @@
  Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=5755552888213791726&amp;p=1&amp;aq=-3369009283499207512&amp;cid=18943&amp;jobAge=668&amp;brelb=15&amp;bscr=52.409454&amp;scr=52.409454</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>c88e76ee05d5f22f3af4</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>30</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:FastAPI, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>88274fcde114523a2947</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=-8489441105830182890&amp;p=1&amp;aq=8882276308265068022&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=52.072277&amp;scr=52.072277</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=11&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=260&amp;brelb=15&amp;scr=28.932817&amp;bscr=28.932817&amp;aq=219138590995434933&amp;elckey=3525813309626419305</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,25 +1962,25 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>c88e76ee05d5f22f3af4</t>
+          <t>2b1b1f1bea326c79719d</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>skill:Python, skill:FastAPI, skill:REST APIs</t>
+          <t>skill:AWS, skill:Terraform</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>65775a6b0ef427ea49eb</t>
+          <t>2027b6d85b723bf1424e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+          <t>&amp;nbsp;...As a  Cloud &lt;b&gt;Engineer &lt;/b&gt;(Backend / &lt;b&gt;DevOps-&lt;/b&gt;leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nb</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=28.985275&amp;bscr=28.985275&amp;aq=-8809178904638934262&amp;elckey=8668378667461621585</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-6062335632225232796&amp;p=1&amp;aq=8295423849965910059&amp;cid=18943&amp;jobAge=260&amp;brelb=15&amp;bscr=30.928972&amp;scr=30.928972</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2033,17 +2033,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2b1b1f1bea326c79719d</t>
+          <t>d322ed2c3af201959570</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2069,17 +2069,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>235ab6b4e3ed60f55361</t>
+          <t>c2cfa9e11927d09e72b1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Smartworking</t>
+          <t>Ping Identity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+          <t>Staff Software Engineer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2088,86 +2088,86 @@
         </is>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...As a  Cloud &lt;b&gt;Engineer &lt;/b&gt;(Backend / &lt;b&gt;DevOps-&lt;/b&gt;leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nb</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-1860585552559655796&amp;p=1&amp;aq=4586418624418592339&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=30.378479&amp;scr=30.378479</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>d322ed2c3af201959570</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>20</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>skill:AWS, skill:Terraform</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>142e4ba47d0fd3e86456</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ping Identity</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Staff Software Engineer</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>&amp;nbsp;...of distributed systems capable of handling rapid global growth while maintaining low latency. 
  Operational Excellence: Partner with &lt;b&gt;SRE &lt;/b&gt;and DevOps to enhance CI/CD pipelines, automated scaling, and self-healing infrastructure. 
  Technical Leadership: Drive rigorous...&amp;nbsp;</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=5&amp;elckey=-2642809006383721881&amp;p=1&amp;aq=4073150113332618941&amp;cid=18943&amp;jobAge=68&amp;relb=100&amp;brelb=100&amp;bscr=737.705&amp;scr=737.705</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:29:45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>c83d35754b7c640725c4</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>skill:CI/CD, skill:Distributed Systems</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>084937782f46eb59fc2d</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Smartworking</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-378987479233205627?ckey=SRE&amp;rgn=55126&amp;pos=3&amp;elckey=2499756351451480399&amp;p=1&amp;aq=7822845172208213070&amp;cid=18943&amp;jobAge=58&amp;relb=100&amp;brelb=100&amp;bscr=725.0664&amp;scr=725.0664</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Operations+Engineer&amp;rgn=55126&amp;pos=18&amp;groupId=73040043&amp;elckey=-2414156722002217437&amp;p=1&amp;aq=2693155508001447441&amp;cid=18943&amp;jobAge=260&amp;brelb=15&amp;bscr=28.909716&amp;scr=28.909716</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 16:32:06</t>
+          <t>2026-09-04 02:29:45</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>c83d35754b7c640725c4</t>
+          <t>2b1b1f1bea326c79719d</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>skill:CI/CD, skill:Distributed Systems</t>
+          <t>skill:AWS, skill:Terraform</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2209,77 +2209,6 @@
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>bcf58527fb7e7facba85</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Smartworking</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cloud Engineer (Backend / DevOps-leaning)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...As a  &lt;b&gt;Cloud Engineer &lt;/b&gt;(Backend / DevOps-leaning) , you will take responsibility for designing, building and maintaining  AWS infrastructure  using  Terraform  and  Infrastructure as Code  . This is an ongoing, long-term opportunity focused on reliable cloud infrastructure...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Operations+Engineer&amp;rgn=55126&amp;pos=15&amp;groupId=73040043&amp;elckey=2728408635832984843&amp;p=1&amp;aq=8381010108530996913&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=29.177908&amp;scr=29.177908</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:32:06</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2b1b1f1bea326c79719d</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>20</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>skill:AWS, skill:Terraform</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
